--- a/Output/BRDM_countarea_ALM_A40_PLStraws.xlsx
+++ b/Output/BRDM_countarea_ALM_A40_PLStraws.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,10 +762,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -872,10 +870,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1055,6 +1051,742 @@
       </c>
       <c r="BN3" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.15925482510997</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.49097356544165</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.321637426900585</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0.7575757575757575</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3174603174603174</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.005711063822048</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5649717514124294</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.326797385620915</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3930817610062893</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>8.420215053284224</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.7816701105001453</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3598484848484849</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>0.7662835249042145</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.289625680013207</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.5543544542380399</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.442002442002442</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.4694835680751174</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.3623188405797101</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.201298701298701</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>1.679357021996616</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.968276608413536</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>11.48373983739837</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.3875968992248062</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>15.99136918435436</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.8161483906164757</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>3.3501221001221</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2.666666666666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4065040650406504</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.361531550210795</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4385964912280702</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.352265043948614</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1.604938271604938</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.326797385620915</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.890149362578085</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5.6396383894544</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.4016064257028113</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.3968253968253969</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.690201112537441</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>2.861026277813203</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.2506265664160401</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.4938271604938271</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3174603174603174</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0.7716049382716049</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.062876266346556</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7092198581560284</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.6964758322886196</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.937984496124031</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.452830188679245</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7936507936507938</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.8841375843745513</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>0.7662835249042145</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4016064257028113</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.5543544542380399</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>2.551942186088528</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>3.934940607690584</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1.688034188034188</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.094132282811529</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.248322391618865</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1.604938271604938</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4474272930648769</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.193673530289466</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7633005114113427</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.645502645502646</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>3.477868112014453</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.3875968992248062</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>4.010451565169524</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.7326007326007327</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,10 +2136,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -1514,10 +2244,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1697,6 +2425,740 @@
       </c>
       <c r="BN3" t="n">
         <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.021662334350362</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.7746025264604</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.120662386471146</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7596939152774259</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2852721653672741</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3174603174603174</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.479178071845988</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5649717514124294</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3267973856209151</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3930817610062894</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7.305233821488584</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.4791985535412051</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2318045648605188</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>0.7662835249042146</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.8262788956079106</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.5543544542380399</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.442002442002442</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.4694835680751174</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.3623188405797101</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.6007224712717714</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.265986323710904</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>0.8397504305870499</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.404416814115811</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.9955490477854414</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>2.572296139101576</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.3875968992248063</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>4.988876515698589</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>8.154929789552327</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.4444444444444445</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.4132014064239494</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.210005626013193</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2.666666666666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4065040650406505</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6866604903520244</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4385964912280701</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.352265043948614</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0.9642283550502044</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.3267973856209151</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.038542399898334</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.445367439674302</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.4016064257028112</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.3968253968253969</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.8469266329862851</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>1.851851851851852</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>1.609989784016765</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>7.7746025264604</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.2506265664160401</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.7751937984496126</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.4938271604938271</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3174603174603174</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0.771604938271605</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.887066133668028</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.265986323710904</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.7092198581560283</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.6964758322886196</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.937984496124031</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9235009052067279</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7936507936507938</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4464698696524947</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>0.7662835249042146</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4016064257028112</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.5543544542380399</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.19047619047619</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>1.412691433878357</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>2.424568486044559</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.8442199258606159</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.273129589435248</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.988876515698589</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.423265964282606</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0.9642283550502044</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4474272930648769</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.193673530289466</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7633005114113427</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.645502645502646</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>1.74989797902534</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.3875968992248063</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.265986323710904</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>0.7903857566676432</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.7326007326007327</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Output/BRDM_countarea_ALM_A40_PLStraws.xlsx
+++ b/Output/BRDM_countarea_ALM_A40_PLStraws.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,6 +1789,374 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4065040650406504</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7326007326007327</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8830409356725145</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4480286738351255</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6802721088435374</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5968367651447329</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.851549931922128</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.229528311506286</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.5128205128205129</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.8230452674897119</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>6.436314363143632</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.7936507936507938</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.333333333333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.465201465201465</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3787878787878787</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0.7575757575757575</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.7589556769884639</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.587301587301587</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7575757575757575</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2923976608187135</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.399183004014518</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.3787878787878787</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.6751738572682465</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>2.664859981933153</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>3.006435500912497</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1800,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,6 +3529,374 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4065040650406504</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7326007326007327</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4415495130061443</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4480286738351255</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6802721088435374</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5968367651447329</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.830150666572052</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.6236048134117524</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.4681389380386036</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.823045267489712</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>0.7191365550176451</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.7936507936507938</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.265986323710904</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0.7751937984496126</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.465201465201465</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3787878787878787</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.758955676988464</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.587301587301587</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2923976608187135</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.316720654622414</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8130081300813008</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.3787878787878787</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.6751738572682465</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>1.60772102353728</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>1.623320955980573</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.3739295009773841</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
